--- a/artfynd/A 25881-2025 artfynd.xlsx
+++ b/artfynd/A 25881-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126181428</v>
       </c>
       <c r="B2" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126181432</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126182030</v>
       </c>
       <c r="B4" t="n">
-        <v>74878</v>
+        <v>74879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126180861</v>
+        <v>126181025</v>
       </c>
       <c r="B5" t="n">
-        <v>98360</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372055</v>
+        <v>372032</v>
       </c>
       <c r="R5" t="n">
-        <v>6707768</v>
+        <v>6707718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126181025</v>
+        <v>126180861</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372032</v>
+        <v>372055</v>
       </c>
       <c r="R6" t="n">
-        <v>6707718</v>
+        <v>6707768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>126180852</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126180953</v>
       </c>
       <c r="B8" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 25881-2025 artfynd.xlsx
+++ b/artfynd/A 25881-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126181432</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126180861</v>
       </c>
       <c r="B6" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25881-2025 artfynd.xlsx
+++ b/artfynd/A 25881-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126181025</v>
+        <v>126180861</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372032</v>
+        <v>372055</v>
       </c>
       <c r="R5" t="n">
-        <v>6707718</v>
+        <v>6707768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126180861</v>
+        <v>126181025</v>
       </c>
       <c r="B6" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372055</v>
+        <v>372032</v>
       </c>
       <c r="R6" t="n">
-        <v>6707768</v>
+        <v>6707718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25881-2025 artfynd.xlsx
+++ b/artfynd/A 25881-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126181432</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126180861</v>
+        <v>126181025</v>
       </c>
       <c r="B5" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372055</v>
+        <v>372032</v>
       </c>
       <c r="R5" t="n">
-        <v>6707768</v>
+        <v>6707718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126181025</v>
+        <v>126180861</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372032</v>
+        <v>372055</v>
       </c>
       <c r="R6" t="n">
-        <v>6707718</v>
+        <v>6707768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25881-2025 artfynd.xlsx
+++ b/artfynd/A 25881-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126181428</v>
       </c>
       <c r="B2" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126181432</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126182030</v>
       </c>
       <c r="B4" t="n">
-        <v>74879</v>
+        <v>74883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126181025</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126180861</v>
       </c>
       <c r="B6" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126180852</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126180953</v>
       </c>
       <c r="B8" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
